--- a/output/pdf_financials_xlsx/MDI.xlsx
+++ b/output/pdf_financials_xlsx/MDI.xlsx
@@ -6362,34 +6362,34 @@
         <v>-44.333</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-1.791</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>10.052</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>25.48</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>50.644</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>61.896</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>86.78700000000001</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>70.021</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>78.783</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>81.64</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>52.614</v>
       </c>
       <c r="N91" s="1" t="inlineStr">
         <is>
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>76.90300000000001</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>75.801</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>77.973</v>
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
@@ -6424,34 +6424,34 @@
         <v>11.142</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.918</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>14.204</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>15.937</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>17.258</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>18.643</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>19.413</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>19.757</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>19.677</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.519</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.559</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6459,13 +6459,13 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.696</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.615</v>
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
@@ -11856,7 +11856,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11943,7 +11947,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -15520,7 +15528,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16120,7 +16132,11 @@
           <t>Share‐based payments reserve</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16413,7 +16429,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16508,7 +16528,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -16694,7 +16718,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MDI.xlsx
+++ b/output/pdf_financials_xlsx/MDI.xlsx
@@ -2515,39 +2515,35 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>58.035</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>30.232</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>37.237</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>82.31100000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>74.244</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>44.897</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>50.228</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>25.975</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>21.256</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>27.366</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>58.433</v>
@@ -2647,39 +2643,35 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>58.035</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>30.232</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>37.237</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>82.31100000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>74.244</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>44.897</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>50.228</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>25.975</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>21.256</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>27.366</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>58.433</v>
@@ -3438,28 +3430,28 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>48.027</v>
+        <v>10.79</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>98.443</v>
+        <v>16.132</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>91.113</v>
+        <v>16.869</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>60.047</v>
+        <v>15.15</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>60.239</v>
+        <v>10.011</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.956</v>
+        <v>8.981</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>28.697</v>
+        <v>7.441</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>36.443</v>
+        <v>9.077</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>8.847</v>
@@ -15152,7 +15144,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">

--- a/output/pdf_financials_xlsx/MDI.xlsx
+++ b/output/pdf_financials_xlsx/MDI.xlsx
@@ -2219,10 +2219,10 @@
         <v>47.478</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>51.718</v>
+        <v>1.054</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>63.519</v>
+        <v>3.676</v>
       </c>
       <c r="R28" s="1" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         <v>145.05</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>122.731</v>
+        <v>72.06699999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>100.819</v>
+        <v>40.976</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         <v>19.71479132630732</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>17.36692260016358</v>
+        <v>10.19776593546853</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>13.8567770647586</v>
+        <v>5.631828296308717</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -7645,40 +7645,40 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.932</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>2.228</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>3.409</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>18.717</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>6.997</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>3.223</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>2.662</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>11.933</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>1.256</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="N112" s="1" t="inlineStr">
         <is>
@@ -7686,13 +7686,13 @@
         </is>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>3.501</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>2.138</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>3.247</v>
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
@@ -22571,7 +22571,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>4.8</v>
       </c>
@@ -26231,7 +26235,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -32890,7 +32898,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -37132,7 +37140,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -37221,7 +37233,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">

--- a/output/pdf_financials_xlsx/MDI.xlsx
+++ b/output/pdf_financials_xlsx/MDI.xlsx
@@ -1340,15 +1340,11 @@
       <c r="K16" s="3" t="n">
         <v>-10.336</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L16" s="3" t="n">
+        <v>-70.962</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>10.034</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1658,15 +1654,11 @@
       <c r="K20" s="3" t="n">
         <v>-18.084</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-70.962</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>10.034</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1850,15 +1842,11 @@
       <c r="K23" s="3" t="n">
         <v>-18.084</v>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L23" s="3" t="n">
+        <v>-70.962</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>10.034</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -2070,15 +2058,11 @@
       <c r="K26" s="3" t="n">
         <v>78.626087</v>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L26" s="3" t="n">
+        <v>80.63863600000001</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>83.61666700000001</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2138,15 +2122,11 @@
       <c r="K27" s="3" t="n">
         <v>-10.336</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>-70.962</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>10.034</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2268,15 +2248,11 @@
       <c r="K29" s="3" t="n">
         <v>30.573</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>-31.42</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>49.194</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2336,15 +2312,11 @@
       <c r="K30" s="3" t="n">
         <v>7.944712100659526</v>
       </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L30" s="3" t="n">
+        <v>-7.679447822771444</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>11.38549699589887</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2404,15 +2376,11 @@
       <c r="K31" s="3" t="n">
         <v>-74.96130030959752</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -2472,15 +2440,11 @@
       <c r="K32" s="3" t="n">
         <v>-4.69931552769852</v>
       </c>
-      <c r="L32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L32" s="3" t="n">
+        <v>-17.34401579883855</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>2.32227663651765</v>
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
@@ -4167,11 +4131,15 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>32.072</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>25.538</v>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D59" s="3" t="n">
         <v>6.295</v>
@@ -6864,15 +6832,11 @@
       <c r="K99" s="3" t="n">
         <v>-18.084</v>
       </c>
-      <c r="L99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L99" s="3" t="n">
+        <v>-70.962</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>10.034</v>
       </c>
       <c r="N99" s="1" t="inlineStr">
         <is>
@@ -8247,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-11.249</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -11173,7 +11137,11 @@
           <t>LEASE LIABILITIES</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -19938,7 +19906,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -22072,7 +22040,11 @@
           <t>Repurchase of common shares (notes 13 and 16)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -23626,7 +23598,11 @@
           <t>Repurchase of common shares (notes 12 and 15)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -30742,7 +30718,11 @@
           <t>Future income tax (recovery)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" s="5" t="n">
         <v>1.328</v>
       </c>
@@ -36079,7 +36059,11 @@
           <t>NET EARNINGS (LOSS) $</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -36384,7 +36368,11 @@
           <t>NET EARNINGS (LOSS) $</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
